--- a/output/topology_excel/14079.xlsx
+++ b/output/topology_excel/14079.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
         <v>7</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>256</v>
+        <v>206</v>
       </c>
       <c r="F14" t="n">
-        <v>206</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>394</v>
+        <v>206</v>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,15 +784,15 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
         <v>8</v>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>286</v>
+        <v>189</v>
       </c>
       <c r="F17" t="n">
-        <v>273</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -828,15 +828,15 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>189</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
         <v>6</v>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -993,21 +993,65 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>180</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>10</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
         <v>176</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>128</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/14079.xlsx
+++ b/output/topology_excel/14079.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
         </is>
       </c>
     </row>
@@ -481,6 +521,14 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +551,14 @@
       <c r="F3" t="n">
         <v>68</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +581,14 @@
       <c r="F4" t="n">
         <v>18</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +611,14 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +641,14 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +671,14 @@
       <c r="F7" t="n">
         <v>10</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +701,14 @@
       <c r="F8" t="n">
         <v>10</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +731,14 @@
       <c r="F9" t="n">
         <v>14</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -655,8 +759,16 @@
         <v>354</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -677,8 +789,16 @@
         <v>508</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +821,14 @@
       <c r="F12" t="n">
         <v>18</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +851,14 @@
       <c r="F13" t="n">
         <v>22</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,14 +873,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +915,14 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -781,14 +937,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>176</v>
+      </c>
+      <c r="H16" t="n">
+        <v>22</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -809,8 +977,16 @@
         <v>189</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -831,8 +1007,16 @@
         <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +1039,14 @@
       <c r="F19" t="n">
         <v>18</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1069,14 @@
       <c r="F20" t="n">
         <v>18</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -897,8 +1097,16 @@
         <v>203</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -913,13 +1121,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>286</v>
+        <v>136</v>
       </c>
       <c r="F22" t="n">
-        <v>273</v>
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>85</v>
+      </c>
+      <c r="H22" t="n">
+        <v>43</v>
+      </c>
+      <c r="I22" t="n">
+        <v>90</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>170</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -943,6 +1175,14 @@
       <c r="F23" t="n">
         <v>18</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -963,8 +1203,16 @@
         <v>394</v>
       </c>
       <c r="F24" t="n">
-        <v>145</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1235,14 @@
       <c r="F25" t="n">
         <v>22</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1265,14 @@
       <c r="F26" t="n">
         <v>16</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1029,8 +1293,16 @@
         <v>176</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1325,14 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
